--- a/БД подпрограмм.xlsx
+++ b/БД подпрограмм.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Название модели</t>
   </si>
@@ -66,6 +66,9 @@
   </si>
   <si>
     <t>Модель Bera с пикапами (3 сорта водорода).</t>
+  </si>
+  <si>
+    <t>насколько я помню, никакой разницы со мной почти не было. То есть 3 сорта водорода здесь ни при чём!</t>
   </si>
 </sst>
 </file>
@@ -722,7 +725,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -731,12 +734,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1090,26 +1087,26 @@
       </c>
     </row>
     <row r="2" ht="76" customHeight="1" spans="1:5">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
     </row>
     <row r="3" ht="65" customHeight="1" spans="1:5">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="4"/>
+      <c r="C3" s="3"/>
       <c r="D3" s="3">
         <v>73</v>
       </c>
@@ -1117,78 +1114,80 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1" spans="1:5">
-      <c r="A4" s="4" t="s">
+    <row r="4" ht="145" customHeight="1" spans="1:5">
+      <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="4"/>
+      <c r="C4" s="3"/>
       <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
+      <c r="E4" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:5">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:5">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:5">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:4">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="6"/>
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:4">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:4">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:4">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:4">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
       <c r="D12" s="3"/>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:4">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
       <c r="D13" s="3"/>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:4">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
       <c r="D14" s="3"/>
     </row>
     <row r="15" ht="28" customHeight="1"/>

--- a/БД подпрограмм.xlsx
+++ b/БД подпрограмм.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Название модели</t>
   </si>
@@ -42,6 +42,18 @@
   </si>
   <si>
     <t>Комментарий</t>
+  </si>
+  <si>
+    <t>TITAN</t>
+  </si>
+  <si>
+    <t>4-флюидная модель без пикапов. Задача RNF-2026-1</t>
+  </si>
+  <si>
+    <t>В этой задаче было проведено сравнение флюидной и кинетической модели для атомов с точки зрения поглощения Layman-alpha</t>
+  </si>
+  <si>
+    <t>Далее решил пересчитать с более слабым сглаживанием ударной волны</t>
   </si>
   <si>
     <t>TITAN_A1</t>
@@ -81,7 +93,7 @@
     <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -99,6 +111,27 @@
     <font>
       <b/>
       <sz val="22"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -595,137 +628,137 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -734,6 +767,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1058,14 +1100,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="23.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="30" style="1" customWidth="1"/>
     <col min="2" max="2" width="128.336363636364" style="1" customWidth="1"/>
-    <col min="3" max="3" width="114" style="1" customWidth="1"/>
+    <col min="3" max="3" width="74.6727272727273" style="1" customWidth="1"/>
     <col min="4" max="4" width="18.7" style="1" customWidth="1"/>
-    <col min="5" max="5" width="52.7272727272727" style="1" customWidth="1"/>
+    <col min="5" max="5" width="55.8454545454545" style="1" customWidth="1"/>
     <col min="6" max="24" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1086,53 +1128,63 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="76" customHeight="1" spans="1:5">
-      <c r="A2" s="3" t="s">
+    <row r="2" ht="80" customHeight="1" spans="1:5">
+      <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-    </row>
-    <row r="3" ht="65" customHeight="1" spans="1:5">
+      <c r="D2" s="3">
+        <v>79</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" ht="76" customHeight="1" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" ht="65" customHeight="1" spans="1:5">
+      <c r="A4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3">
         <v>73</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" ht="145" customHeight="1" spans="1:5">
-      <c r="A4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
       <c r="E4" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:5">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" ht="145" customHeight="1" spans="1:5">
+      <c r="A5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
+      <c r="E5" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:5">
       <c r="A6" s="3"/>
@@ -1148,17 +1200,18 @@
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" ht="28" customHeight="1" spans="1:4">
+    <row r="8" ht="28" customHeight="1" spans="1:5">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:4">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:4">
       <c r="A10" s="3"/>
@@ -1190,7 +1243,12 @@
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
     </row>
-    <row r="15" ht="28" customHeight="1"/>
+    <row r="15" ht="28" customHeight="1" spans="1:4">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+    </row>
     <row r="16" ht="28" customHeight="1"/>
     <row r="17" ht="28" customHeight="1"/>
     <row r="18" ht="28" customHeight="1"/>
@@ -1230,6 +1288,7 @@
     <row r="52" ht="28" customHeight="1"/>
     <row r="53" ht="28" customHeight="1"/>
     <row r="54" ht="28" customHeight="1"/>
+    <row r="55" ht="28" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/БД подпрограмм.xlsx
+++ b/БД подпрограмм.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Название модели</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>Я предполагаю, что роль пикапов у Bera переоценена. Я думаю, что так происходит из-за малого количества сортов атомов.</t>
+  </si>
+  <si>
+    <t>Кажется что количество сортов атомов не при чём</t>
   </si>
   <si>
     <t>TITAN_A2</t>
@@ -1156,34 +1159,36 @@
         <v>11</v>
       </c>
       <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
+      <c r="E3" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="4" ht="65" customHeight="1" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3">
         <v>73</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" ht="145" customHeight="1" spans="1:5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" ht="49" customHeight="1" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:5">

--- a/БД подпрограмм.xlsx
+++ b/БД подпрограмм.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10400"/>
+    <workbookView windowWidth="23040" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1104,13 +1104,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E55"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="23.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="23.4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="30" style="1" customWidth="1"/>
-    <col min="2" max="2" width="128.336363636364" style="1" customWidth="1"/>
-    <col min="3" max="3" width="74.6727272727273" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.7" style="1" customWidth="1"/>
-    <col min="5" max="5" width="55.8454545454545" style="1" customWidth="1"/>
+    <col min="2" max="2" width="128.333333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="74.6759259259259" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.7037037037037" style="1" customWidth="1"/>
+    <col min="5" max="5" width="71.2685185185185" style="1" customWidth="1"/>
     <col min="6" max="24" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1178,7 +1178,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" ht="49" customHeight="1" spans="1:5">
+    <row r="5" ht="78" customHeight="1" spans="1:5">
       <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
@@ -1191,7 +1191,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1" spans="1:5">
+    <row r="6" ht="78" customHeight="1" spans="1:5">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -1212,43 +1212,43 @@
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
     </row>
-    <row r="9" ht="28" customHeight="1" spans="1:4">
+    <row r="9" ht="28" customHeight="1" spans="1:5">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
     </row>
-    <row r="10" ht="28" customHeight="1" spans="1:4">
+    <row r="10" ht="28" customHeight="1" spans="1:5">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" ht="28" customHeight="1" spans="1:4">
+    <row r="11" ht="28" customHeight="1" spans="1:5">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" ht="28" customHeight="1" spans="1:4">
+    <row r="12" ht="28" customHeight="1" spans="1:5">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
     </row>
-    <row r="13" ht="28" customHeight="1" spans="1:4">
+    <row r="13" ht="28" customHeight="1" spans="1:5">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
     </row>
-    <row r="14" ht="28" customHeight="1" spans="1:4">
+    <row r="14" ht="28" customHeight="1" spans="1:5">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
     </row>
-    <row r="15" ht="28" customHeight="1" spans="1:4">
+    <row r="15" ht="28" customHeight="1" spans="1:5">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>

--- a/БД подпрограмм.xlsx
+++ b/БД подпрограмм.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="25600" windowHeight="9880"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Название модели</t>
   </si>
@@ -53,37 +53,46 @@
     <t>В этой задаче было проведено сравнение флюидной и кинетической модели для атомов с точки зрения поглощения Layman-alpha</t>
   </si>
   <si>
-    <t>Далее решил пересчитать с более слабым сглаживанием ударной волны</t>
+    <t>79 (может 80)</t>
+  </si>
+  <si>
+    <t>Далее решил пересчитать с более слабым сглаживанием ударной волны. Фактически результаты не поменялись. 79-80 это рабочая флюидная модель без пикапов. Сначала модель была посчитана с неправильным сечением (такое сечение осталось в работе по диссипации и в работе в MNRAS по токам) - потом она была пересчитана с правильным для статьи RNF1</t>
   </si>
   <si>
     <t>TITAN_A1</t>
   </si>
   <si>
-    <t>Посчитать мою модель с флюидными пикапами (9 сортов водорода).</t>
+    <t>Модель с флюидными пикапами (9 сортов водорода).</t>
+  </si>
+  <si>
+    <t>Рабочая флюидная модель</t>
+  </si>
+  <si>
+    <t>TITAN_A2</t>
+  </si>
+  <si>
+    <t>Модель без пикапов но с подходом Bera (3 сорта водорода).</t>
+  </si>
+  <si>
+    <t>Разницы с моим подходои почти нет, зато этот работает быстрее</t>
+  </si>
+  <si>
+    <t>TITAN_A3</t>
+  </si>
+  <si>
+    <t>Модель Bera с пикапами (3 сорта водорода).</t>
   </si>
   <si>
     <t>Я предполагаю, что роль пикапов у Bera переоценена. Я думаю, что так происходит из-за малого количества сортов атомов.</t>
   </si>
   <si>
-    <t>Кажется что количество сортов атомов не при чём</t>
-  </si>
-  <si>
-    <t>TITAN_A2</t>
-  </si>
-  <si>
-    <t>Посчитать мою модель без пикапов но с подходом Bera (3 сорта водорода).</t>
-  </si>
-  <si>
-    <t>Разницы с моим подходои почти нет, зато этот работает быстрее</t>
-  </si>
-  <si>
-    <t>TITAN_A3</t>
-  </si>
-  <si>
-    <t>Модель Bera с пикапами (3 сорта водорода).</t>
-  </si>
-  <si>
     <t>насколько я помню, никакой разницы со мной почти не было. То есть 3 сорта водорода здесь ни при чём!</t>
+  </si>
+  <si>
+    <t>TITAN_A4</t>
+  </si>
+  <si>
+    <t>Модель с кинетическими пикапами и водородом (9 сортов + 2 pui)</t>
   </si>
 </sst>
 </file>
@@ -1104,13 +1113,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E55"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="23.4" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="23.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="30" style="1" customWidth="1"/>
-    <col min="2" max="2" width="128.333333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="74.6759259259259" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.7037037037037" style="1" customWidth="1"/>
-    <col min="5" max="5" width="71.2685185185185" style="1" customWidth="1"/>
+    <col min="2" max="2" width="128.336363636364" style="1" customWidth="1"/>
+    <col min="3" max="3" width="74.6727272727273" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.7" style="1" customWidth="1"/>
+    <col min="5" max="5" width="184.409090909091" style="1" customWidth="1"/>
     <col min="6" max="24" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1141,24 +1150,24 @@
       <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="3">
-        <v>79</v>
+      <c r="D2" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" ht="76" customHeight="1" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3">
+        <v>81</v>
+      </c>
       <c r="E3" s="3" t="s">
         <v>12</v>
       </c>
@@ -1185,15 +1194,21 @@
       <c r="B5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="3"/>
+      <c r="C5" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" ht="78" customHeight="1" spans="1:5">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
+      <c r="A6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>

--- a/БД подпрограмм.xlsx
+++ b/БД подпрограмм.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="9880"/>
+    <workbookView windowWidth="23040" windowHeight="8580"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Название модели</t>
   </si>
@@ -93,6 +93,12 @@
   </si>
   <si>
     <t>Модель с кинетическими пикапами и водородом (9 сортов + 2 pui)</t>
+  </si>
+  <si>
+    <t>TITAN_A5</t>
+  </si>
+  <si>
+    <t>Проект Aeolus - моделирование O-звёзд</t>
   </si>
 </sst>
 </file>
@@ -1113,13 +1119,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E55"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="23.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="23.4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="30" style="1" customWidth="1"/>
-    <col min="2" max="2" width="128.336363636364" style="1" customWidth="1"/>
-    <col min="3" max="3" width="74.6727272727273" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.7" style="1" customWidth="1"/>
-    <col min="5" max="5" width="184.409090909091" style="1" customWidth="1"/>
+    <col min="2" max="2" width="128.333333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="74.6759259259259" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.7037037037037" style="1" customWidth="1"/>
+    <col min="5" max="5" width="184.407407407407" style="1" customWidth="1"/>
     <col min="6" max="24" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1213,9 +1219,13 @@
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
     </row>
-    <row r="7" ht="28" customHeight="1" spans="1:5">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
+    <row r="7" ht="66" customHeight="1" spans="1:5">
+      <c r="A7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>

--- a/БД подпрограмм.xlsx
+++ b/БД подпрограмм.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8580"/>
+    <workbookView windowWidth="28800" windowHeight="12360"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Название модели</t>
   </si>
@@ -99,6 +99,12 @@
   </si>
   <si>
     <t>Проект Aeolus - моделирование O-звёзд</t>
+  </si>
+  <si>
+    <t>TITAN_A6</t>
+  </si>
+  <si>
+    <t>Проект Astrail - пересоединение на гелиопаузе - изначально получена из задачи TITAN</t>
   </si>
 </sst>
 </file>
@@ -1230,9 +1236,13 @@
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" ht="28" customHeight="1" spans="1:5">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
+    <row r="8" ht="56" customHeight="1" spans="1:5">
+      <c r="A8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>

--- a/БД подпрограмм.xlsx
+++ b/БД подпрограмм.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>Название модели</t>
   </si>
@@ -114,6 +114,12 @@
   </si>
   <si>
     <t xml:space="preserve">посмотреть положение BS </t>
+  </si>
+  <si>
+    <t>TITAN_A8</t>
+  </si>
+  <si>
+    <t>Из TITAN_A7, но нет пикапов сорта 2 во внутреннем ударном слое и нет пикапов во внешнем ударном слое</t>
   </si>
 </sst>
 </file>
@@ -643,10 +649,16 @@
       </c>
       <c r="D9" s="7"/>
     </row>
-    <row r="10" spans="1:5" ht="28" customHeight="1">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
+    <row r="10" spans="1:5" ht="58" customHeight="1">
+      <c r="A10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>28</v>
+      </c>
       <c r="D10" s="3"/>
     </row>
     <row r="11" spans="1:5" ht="28" customHeight="1">

--- a/БД подпрограмм.xlsx
+++ b/БД подпрограмм.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19420" windowHeight="11020"/>
+    <workbookView windowWidth="30720" windowHeight="13440"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
   <si>
     <t>Название модели</t>
   </si>
@@ -120,13 +120,28 @@
   </si>
   <si>
     <t>Из TITAN_A7, но нет пикапов сорта 2 во внутреннем ударном слое и нет пикапов во внешнем ударном слое</t>
+  </si>
+  <si>
+    <t>TITAN_A9</t>
+  </si>
+  <si>
+    <t>Беру модель TITAN - и во внутреннем ударном слое увеличиваю охлаждение на 30%</t>
+  </si>
+  <si>
+    <t>посмотреть, что увеличение охлаждения на 30%очень слабо влияет на ударный слой</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-* #\.##0.00_-;\-* #\.##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-* #\.##0.00\ &quot;₽&quot;_-;\-* #\.##0.00\ &quot;₽&quot;_-;_-* \-??\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,16 +185,346 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -215,9 +560,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -243,10 +830,57 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Запятая" xfId="1" builtinId="3"/>
+    <cellStyle name="Денежный" xfId="2" builtinId="4"/>
+    <cellStyle name="Процент" xfId="3" builtinId="5"/>
+    <cellStyle name="Запятая [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Денежный [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Гиперссылка" xfId="6" builtinId="8"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="7" builtinId="9"/>
+    <cellStyle name="Примечание" xfId="8" builtinId="10"/>
+    <cellStyle name="Предупреждающий текст" xfId="9" builtinId="11"/>
+    <cellStyle name="Заголовок" xfId="10" builtinId="15"/>
+    <cellStyle name="Пояснительный текст" xfId="11" builtinId="53"/>
+    <cellStyle name="Заголовок 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Заголовок 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Заголовок 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Заголовок 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Ввод" xfId="16" builtinId="20"/>
+    <cellStyle name="Вывод" xfId="17" builtinId="21"/>
+    <cellStyle name="Вычисление" xfId="18" builtinId="22"/>
+    <cellStyle name="Проверить ячейку" xfId="19" builtinId="23"/>
+    <cellStyle name="Связанная ячейка" xfId="20" builtinId="24"/>
+    <cellStyle name="Итого" xfId="21" builtinId="25"/>
+    <cellStyle name="Хороший" xfId="22" builtinId="26"/>
+    <cellStyle name="Плохой" xfId="23" builtinId="27"/>
+    <cellStyle name="Нейтральный" xfId="24" builtinId="28"/>
+    <cellStyle name="Акцент1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% — Акцент1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% — Акцент1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% — Акцент1" xfId="28" builtinId="32"/>
+    <cellStyle name="Акцент2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% — Акцент2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% — Акцент2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% — Акцент2" xfId="32" builtinId="36"/>
+    <cellStyle name="Акцент3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% — Акцент3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% — Акцент3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% — Акцент3" xfId="36" builtinId="40"/>
+    <cellStyle name="Акцент4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% — Акцент4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% — Акцент4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% — Акцент4" xfId="40" builtinId="44"/>
+    <cellStyle name="Акцент5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% — Акцент5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% — Акцент5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% — Акцент5" xfId="44" builtinId="48"/>
+    <cellStyle name="Акцент6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% — Акцент6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% — Акцент6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% — Акцент6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -508,24 +1142,24 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X55"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="23.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="23.4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="30" style="1" customWidth="1"/>
-    <col min="2" max="2" width="128.36328125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="74.6328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.7265625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="184.36328125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="128.361111111111" style="1" customWidth="1"/>
+    <col min="3" max="3" width="74.6296296296296" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.7222222222222" style="1" customWidth="1"/>
+    <col min="5" max="5" width="184.361111111111" style="1" customWidth="1"/>
     <col min="6" max="24" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="80" customHeight="1">
+    <row r="1" ht="80" customHeight="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -542,7 +1176,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="80" customHeight="1">
+    <row r="2" ht="80" customHeight="1" spans="1:5">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -559,7 +1193,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="76" customHeight="1">
+    <row r="3" ht="76" customHeight="1" spans="1:5">
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
@@ -574,7 +1208,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="65" customHeight="1">
+    <row r="4" ht="65" customHeight="1" spans="1:5">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
@@ -589,7 +1223,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="78" customHeight="1">
+    <row r="5" ht="78" customHeight="1" spans="1:5">
       <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
@@ -604,7 +1238,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="78" customHeight="1">
+    <row r="6" ht="78" customHeight="1" spans="1:5">
       <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
@@ -615,7 +1249,7 @@
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
     </row>
-    <row r="7" spans="1:5" ht="66" customHeight="1">
+    <row r="7" ht="66" customHeight="1" spans="1:5">
       <c r="A7" s="3" t="s">
         <v>22</v>
       </c>
@@ -626,7 +1260,7 @@
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:5" ht="56" customHeight="1">
+    <row r="8" ht="56" customHeight="1" spans="1:5">
       <c r="A8" s="3" t="s">
         <v>24</v>
       </c>
@@ -637,7 +1271,7 @@
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
     </row>
-    <row r="9" spans="1:5" ht="41.5" customHeight="1">
+    <row r="9" ht="41.5" customHeight="1" spans="1:5">
       <c r="A9" s="3" t="s">
         <v>26</v>
       </c>
@@ -649,7 +1283,7 @@
       </c>
       <c r="D9" s="7"/>
     </row>
-    <row r="10" spans="1:5" ht="58" customHeight="1">
+    <row r="10" ht="58" customHeight="1" spans="1:5">
       <c r="A10" s="3" t="s">
         <v>29</v>
       </c>
@@ -661,47 +1295,53 @@
       </c>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" spans="1:5" ht="28" customHeight="1">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
+    <row r="11" ht="71" customHeight="1" spans="1:5">
+      <c r="A11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:5" ht="28" customHeight="1">
+    <row r="12" ht="71" customHeight="1" spans="1:5">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
     </row>
-    <row r="13" spans="1:5" ht="28" customHeight="1">
+    <row r="13" ht="71" customHeight="1" spans="1:5">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
     </row>
-    <row r="14" spans="1:5" ht="28" customHeight="1">
+    <row r="14" ht="71" customHeight="1" spans="1:5">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
     </row>
-    <row r="15" spans="1:5" ht="28" customHeight="1">
+    <row r="15" ht="71" customHeight="1" spans="1:5">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
     </row>
-    <row r="16" spans="1:5" ht="28" customHeight="1"/>
-    <row r="17" ht="28" customHeight="1"/>
-    <row r="18" ht="28" customHeight="1"/>
-    <row r="19" ht="28" customHeight="1"/>
-    <row r="20" ht="28" customHeight="1"/>
-    <row r="21" ht="28" customHeight="1"/>
-    <row r="22" ht="28" customHeight="1"/>
-    <row r="23" ht="28" customHeight="1"/>
-    <row r="24" ht="28" customHeight="1"/>
-    <row r="25" ht="28" customHeight="1"/>
-    <row r="26" ht="28" customHeight="1"/>
+    <row r="16" ht="71" customHeight="1"/>
+    <row r="17" ht="71" customHeight="1"/>
+    <row r="18" ht="71" customHeight="1"/>
+    <row r="19" ht="71" customHeight="1"/>
+    <row r="20" ht="71" customHeight="1"/>
+    <row r="21" ht="71" customHeight="1"/>
+    <row r="22" ht="71" customHeight="1"/>
+    <row r="23" ht="71" customHeight="1"/>
+    <row r="24" ht="71" customHeight="1"/>
+    <row r="25" ht="71" customHeight="1"/>
+    <row r="26" ht="71" customHeight="1"/>
     <row r="27" ht="28" customHeight="1"/>
     <row r="28" ht="28" customHeight="1"/>
     <row r="29" ht="28" customHeight="1"/>
@@ -733,5 +1373,6 @@
     <row r="55" ht="28" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>